--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -1,106 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AiGraph" sheetId="1" r:id="rId1"/>
+    <sheet name="AiGraph" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>AiGraph</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>fde610e680d06f92</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>initial_state_id</t>
-  </si>
-  <si>
-    <t>automatic_transition_budget</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;AiState.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -413,112 +407,363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AiGraph</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fde610e680d06f92</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>initial_state_id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>automatic_transition_budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>initial_state_id</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>automatic_transition_budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ref&lt;AiState.id&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>13002</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>13003</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>13004</v>
+      </c>
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>13005</v>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>13006</v>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>13007</v>
+      </c>
+      <c r="C14" t="n">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>13008</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13009</v>
+      </c>
+      <c r="C16" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13010</v>
+      </c>
+      <c r="C17" t="n">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>13011</v>
+      </c>
+      <c r="C18" t="n">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>13012</v>
+      </c>
+      <c r="C19" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>13013</v>
+      </c>
+      <c r="C20" t="n">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>13014</v>
+      </c>
+      <c r="C21" t="n">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>13015</v>
+      </c>
+      <c r="C22" t="n">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>13016</v>
+      </c>
+      <c r="C23" t="n">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>13017</v>
+      </c>
+      <c r="C24" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>22</v>
+      <c r="D24" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,6 +766,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980010</v>
+      </c>
+      <c r="C25" t="n">
+        <v>980701</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980011</v>
+      </c>
+      <c r="C26" t="n">
+        <v>980706</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980012</v>
+      </c>
+      <c r="C27" t="n">
+        <v>980711</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>990010</v>
+      </c>
+      <c r="C28" t="n">
+        <v>990701</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>990011</v>
+      </c>
+      <c r="C29" t="n">
+        <v>990704</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>990012</v>
+      </c>
+      <c r="C30" t="n">
+        <v>990707</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +832,28 @@
         <v>8</v>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1000701</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1000706</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,6 +854,17 @@
         <v>8</v>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1010701</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,6 +865,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1020701</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1020705</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1020711</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1030701</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1030704</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1030710</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1040701</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1040705</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1040715</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,17 @@
         <v>8</v>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1050701</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,6 +975,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1060701</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1060721</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1060741</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1008,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1070701</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1070705</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1070709</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1041,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1080701</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1080705</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1080710</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,6 +1074,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1090041</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1094101</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1094102</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1094106</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1094110</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1094112</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1094113</v>
+      </c>
+      <c r="D58" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1094116</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1094122</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1094126</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1094127</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1094131</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1094136</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1206,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1104101</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1100042</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1104104</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1104105</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1104107</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1104111</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1104112</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1104114</v>
+      </c>
+      <c r="D71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1104118</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1104122</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1104127</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1104132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1104133</v>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,6 +1338,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1114101</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1110042</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1114104</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1114105</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1114109</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1114113</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1114116</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1114117</v>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1114118</v>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1114119</v>
+      </c>
+      <c r="D85" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1114120</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1114121</v>
+      </c>
+      <c r="D87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1114126</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1470,6 +1470,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1120041</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1124101</v>
+      </c>
+      <c r="D89" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1120042</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1124102</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1124103</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1124110</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1124113</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1124114</v>
+      </c>
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1124116</v>
+      </c>
+      <c r="D95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1124118</v>
+      </c>
+      <c r="D96" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1124119</v>
+      </c>
+      <c r="D97" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1124120</v>
+      </c>
+      <c r="D98" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1124122</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1124123</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1602,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1134101</v>
+      </c>
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1134105</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1134106</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1134110</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1134114</v>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1134118</v>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1134120</v>
+      </c>
+      <c r="D107" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1134121</v>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1134125</v>
+      </c>
+      <c r="D109" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1134126</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1134130</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1134134</v>
+      </c>
+      <c r="D112" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,6 +1734,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1140041</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1144101</v>
+      </c>
+      <c r="D113" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1144102</v>
+      </c>
+      <c r="D114" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1144105</v>
+      </c>
+      <c r="D115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1144108</v>
+      </c>
+      <c r="D116" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1144111</v>
+      </c>
+      <c r="D117" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1144114</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1144117</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1144120</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1144122</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1144124</v>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1144126</v>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1144128</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,6 +1866,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1154101</v>
+      </c>
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1154106</v>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1154107</v>
+      </c>
+      <c r="D127" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiGraph.xlsx
+++ b/config/data/AiGraph.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,6 +766,1139 @@
         <v>8</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980010</v>
+      </c>
+      <c r="C25" t="n">
+        <v>980701</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980011</v>
+      </c>
+      <c r="C26" t="n">
+        <v>980706</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980012</v>
+      </c>
+      <c r="C27" t="n">
+        <v>980711</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>990010</v>
+      </c>
+      <c r="C28" t="n">
+        <v>990701</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>990011</v>
+      </c>
+      <c r="C29" t="n">
+        <v>990704</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>990012</v>
+      </c>
+      <c r="C30" t="n">
+        <v>990707</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1000701</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1000706</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1010701</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1020701</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1020705</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1020711</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1030701</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1030704</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1030710</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1040701</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1040705</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1040715</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1050701</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1060701</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1060721</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1060741</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1070701</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1070705</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1070709</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1080701</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1080705</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1080710</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1090041</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1094101</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1094102</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1094106</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1094110</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1094112</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1094113</v>
+      </c>
+      <c r="D58" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1094116</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1094122</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1094126</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1094127</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1094131</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1094136</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1104101</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1100042</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1104104</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1104105</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1104107</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1104111</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1104112</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1104114</v>
+      </c>
+      <c r="D71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1104118</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1104122</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1104127</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1104132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1104133</v>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1114101</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1110042</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1114104</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1114105</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1114109</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1114113</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1114116</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1114117</v>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1114118</v>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1114119</v>
+      </c>
+      <c r="D85" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1114120</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1114121</v>
+      </c>
+      <c r="D87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1114126</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1120041</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1124101</v>
+      </c>
+      <c r="D89" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1120042</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1124102</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1124103</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1124110</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1124113</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1124114</v>
+      </c>
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1124116</v>
+      </c>
+      <c r="D95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1124118</v>
+      </c>
+      <c r="D96" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1124119</v>
+      </c>
+      <c r="D97" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1124120</v>
+      </c>
+      <c r="D98" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1124122</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1124123</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1134101</v>
+      </c>
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1134105</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1134106</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1134110</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1134114</v>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1134118</v>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1134120</v>
+      </c>
+      <c r="D107" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1134121</v>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1134125</v>
+      </c>
+      <c r="D109" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1134126</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1134130</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1134134</v>
+      </c>
+      <c r="D112" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1140041</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1144101</v>
+      </c>
+      <c r="D113" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1144102</v>
+      </c>
+      <c r="D114" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1144105</v>
+      </c>
+      <c r="D115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1144108</v>
+      </c>
+      <c r="D116" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1144111</v>
+      </c>
+      <c r="D117" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1144114</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1144117</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1144120</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1144122</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1144124</v>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1144126</v>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1144128</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1154101</v>
+      </c>
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1154106</v>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1154107</v>
+      </c>
+      <c r="D127" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
